--- a/.agents/skills/proto/assets/Adventure_template/split_xlsx/mystery_box.xlsx
+++ b/.agents/skills/proto/assets/Adventure_template/split_xlsx/mystery_box.xlsx
@@ -47,7 +47,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -69,11 +69,44 @@
         <color rgb="00B7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -84,6 +117,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -547,7 +581,7 @@
           <t>object</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n"/>
+      <c r="K3" s="4" t="n"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>int</t>
@@ -601,7 +635,7 @@
           <t>rand_reward</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n"/>
+      <c r="K4" s="4" t="n"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>id</t>
@@ -660,114 +694,344 @@
       </c>
       <c r="L5" s="1" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>classname</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>meta_info</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>rand_reward</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_2.proto.js</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_2.proto.js</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>Adventure_3_Sport_Box_2</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Теннисная коробка с подарками</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Содержит: 2 бустера для мгновенной уборки мусора со всех горшков в локации, 15 оживителей, 15 ускорителей, 20 жетонов</t>
         </is>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>money_alt</t>
         </is>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>plan=first</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="K9" s="1" t="inlineStr">
         <is>
           <t>[{"asset":"Stuff_Booster_CleanPot","amount":2},{"asset":"RecoverPlantBooster","amount":15},{"asset":"AccelerationPlantBooster","amount":15},{"asset":"AccelerateCraftingBooster","amount":20},{"asset":"Shop_of_miracles_GR_1","amount":30}]</t>
         </is>
       </c>
-      <c r="L6" s="1" t="n"/>
+      <c r="L9" s="1" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>classname</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>meta_info</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>rand_reward</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_3.proto.js</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>/mystery_box/Adventure/Adventure_3_Sport_Box_3.proto.js</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>Adventure_3_Sport_Box_3</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Баскетбольная коробка с подарками</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Коробка содержит: 4 бустеров для мгновенной уборки мусора со всех горшков в локации, 20 оживителей, 20 ускорителей, 30 жетонов</t>
         </is>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>money_alt</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>plan=first</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>[{"asset":"Stuff_Booster_CleanPot","amount":4},{"asset":"RecoverPlantBooster","amount":20},{"asset":"AccelerationPlantBooster","amount":20},{"asset":"AccelerateCraftingBooster","amount":30},{"asset":"Shop_of_miracles_GR_1","amount":50}]</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n"/>
+      <c r="L13" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
